--- a/secciones/valuacion/modelos/Mallplaza_Figuras_Valuacion_recalc.xlsx
+++ b/secciones/valuacion/modelos/Mallplaza_Figuras_Valuacion_recalc.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -709,7 +709,7 @@
     <t xml:space="preserve">Spread nuestra WACC − BCU 10 (pb, real)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lectura: a CLP 3.555 la WACC real implícita (~4,4%) supera en solo ~80 pb al costo real de la deuda de la propia Mallplaza (3,6%).</t>
+    <t xml:space="preserve">Lectura: a CLP 3.555 la WACC real implícita (~4.5%) supera el bono UF a 10 años del BCCh (2.5% real) y queda bajo la WACC de la tasación (5.55% real).</t>
   </si>
   <si>
     <t xml:space="preserve">Eso implica que el patrimonio (78% del capital) casi no recibe prima sobre un bono corporativo AA+: un premio por riesgo difícil de sostener.</t>
@@ -883,7 +883,7 @@
     <t xml:space="preserve">Valor DCF: réplica del DCF v2 escalando la inversión en capital de trabajo de todos los períodos y del año terminal (base = CLP 1.856,8).</t>
   </si>
   <si>
-    <t xml:space="preserve">Lectura: todo el capital de trabajo vale ~CLP 32 por acción (1,7% del DCF). El valor no depende de este supuesto.</t>
+    <t xml:space="preserve">Lectura: todo el capital de trabajo vale ~CLP 33 por acción (1.8% del DCF). El valor no depende de este supuesto.</t>
   </si>
   <si>
     <t xml:space="preserve">Limitación (v2): las CxP comerciales incluyen proveedores de obras (capex); sin la nota de desglose no se separan.</t>
@@ -982,7 +982,7 @@
     <t xml:space="preserve">Valores −1% a +1% coinciden con v2 Sensibilidad (g 3,0%). Fuera de ese rango: réplica del DCF, mismo método (desplazamiento paralelo de la WACC por período).</t>
   </si>
   <si>
-    <t xml:space="preserve">Mensaje: para justificar CLP 3.555 el mercado debe descontar a ~7,6% nominal (~4,4% real), 285 pb bajo nuestra WACC (ver V2).</t>
+    <t xml:space="preserve">Mensaje: para justificar CLP 3.555 el mercado debe descontar a ~7.60% nominal (~4.5% real). 281 pb bajo nuestra WACC terminal.</t>
   </si>
   <si>
     <t xml:space="preserve">V7 — Múltiplos: por qué Chile pesa 70%</t>
@@ -1390,7 +1390,7 @@
     <t xml:space="preserve">Valor DCF si se usara el bono en pesos (CLP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Réplica del DCF v2 con WACC −107 pb en todos los períodos</t>
+    <t xml:space="preserve">Réplica del DCF v4 con WACC -107 pb en todos los períodos</t>
   </si>
   <si>
     <t xml:space="preserve">Precio objetivo 80/20 en ese caso (CLP)</t>
@@ -1399,7 +1399,7 @@
     <t xml:space="preserve">Por qué UST + CRP y no el bono en pesos: (1) el bono local ya trae riesgo Chile, y sumarle el CRP lo contaría dos veces; (2) un 28% de los ingresos viene de Perú y Colombia, cuyo riesgo se agrega con el CRP ponderado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Es la elección más conservadora: con el bono en pesos el precio objetivo sube a ~CLP 2.439, todavía 31% bajo el precio de CLP 3.555. La recomendación no cambia.</t>
+    <t xml:space="preserve">Es la elección más conservadora: con el bono en pesos el precio objetivo sube a ~CLP 2.449. todavía 31% bajo el precio.</t>
   </si>
   <si>
     <t xml:space="preserve">Argumento aislado (posterior): al 1-oct-26 el bono en pesos a 10 años llegó a 6,25%, acercándose a la base del modelo (anexo macro).</t>
@@ -2183,11 +2183,11 @@
         <v>0.064138867416108</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>5051</v>
+        <v>5121.7</v>
       </c>
       <c r="D5" s="12" t="n">
         <f aca="false">0.8*C5+0.2*2951.38547083101</f>
-        <v>4631.0770941662</v>
+        <v>4687.6370941662</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>3555</v>
@@ -2202,11 +2202,11 @@
         <v>0.069138867416108</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4290</v>
+        <v>4344.6</v>
       </c>
       <c r="D6" s="12" t="n">
         <f aca="false">0.8*C6+0.2*2951.38547083101</f>
-        <v>4022.2770941662</v>
+        <v>4065.9570941662</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>3555</v>
@@ -2221,11 +2221,11 @@
         <v>0.074138867416108</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3703</v>
+        <v>3744.8</v>
       </c>
       <c r="D7" s="12" t="n">
         <f aca="false">0.8*C7+0.2*2951.38547083101</f>
-        <v>3552.6770941662</v>
+        <v>3586.1170941662</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>3555</v>
@@ -2240,11 +2240,11 @@
         <v>0.079138867416108</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3237</v>
+        <v>3268.1</v>
       </c>
       <c r="D8" s="12" t="n">
         <f aca="false">0.8*C8+0.2*2951.38547083101</f>
-        <v>3179.8770941662</v>
+        <v>3204.7570941662</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>3555</v>
@@ -2259,11 +2259,11 @@
         <v>0.084138867416108</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2857</v>
+        <v>2880.4</v>
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">0.8*C9+0.2*2951.38547083101</f>
-        <v>2875.8770941662</v>
+        <v>2894.5970941662</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>3555</v>
@@ -2278,11 +2278,11 @@
         <v>0.089138867416108</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2543</v>
+        <v>2559</v>
       </c>
       <c r="D10" s="12" t="n">
         <f aca="false">0.8*C10+0.2*2951.38547083101</f>
-        <v>2624.6770941662</v>
+        <v>2637.4770941662</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>3555</v>
@@ -2297,11 +2297,11 @@
         <v>0.094138867416108</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2278</v>
+        <v>2288.5</v>
       </c>
       <c r="D11" s="12" t="n">
         <f aca="false">0.8*C11+0.2*2951.38547083101</f>
-        <v>2412.6770941662</v>
+        <v>2421.0770941662</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>3555</v>
@@ -2316,11 +2316,11 @@
         <v>0.099138867416108</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2052</v>
+        <v>2057.7</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">0.8*C12+0.2*2951.38547083101</f>
-        <v>2231.8770941662</v>
+        <v>2236.4370941662</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>3555</v>
@@ -2335,11 +2335,11 @@
         <v>0.104138867416108</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1857</v>
+        <v>1858.7</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">0.8*C13+0.2*2951.38547083101</f>
-        <v>2075.8770941662</v>
+        <v>2077.2370941662</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>3555</v>
@@ -2354,11 +2354,11 @@
         <v>0.109138867416108</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1687</v>
+        <v>1685.3</v>
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">0.8*C14+0.2*2951.38547083101</f>
-        <v>1939.8770941662</v>
+        <v>1938.5170941662</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>3555</v>
@@ -2373,11 +2373,11 @@
         <v>0.114138867416108</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="D15" s="12" t="n">
         <f aca="false">0.8*C15+0.2*2951.38547083101</f>
-        <v>1820.6770941662</v>
+        <v>1816.6770941662</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>3555</v>
@@ -2388,7 +2388,7 @@
         <v>310</v>
       </c>
       <c r="B17" s="17" t="n">
-        <v>0.0756146197226035</v>
+        <v>0.0760014740197905</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>311</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">(B17-0.104138867416108)*10000</f>
-        <v>-285.242476935045</v>
+        <v>-281.373933963175</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2408,7 +2408,7 @@
         <v>313</v>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.0741153260304354</v>
+        <v>0.0745082005833657</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>314</v>
@@ -4190,7 +4190,7 @@
         <v>451</v>
       </c>
       <c r="B77" s="11" t="n">
-        <v>2311</v>
+        <v>2323</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>452</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B78" s="12" t="n">
         <f aca="false">0.8*B77+0.2*2951.38547083101</f>
-        <v>2439.0770941662</v>
+        <v>2448.6770941662</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4976,13 +4976,13 @@
         <v>182</v>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1686.94389181781</v>
+        <v>1685.26566288299</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2051.79933329428</v>
+        <v>2057.71807392741</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1856.81199718015</v>
+        <v>1858.65339722933</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>183</v>
@@ -4993,13 +4993,13 @@
         <v>184</v>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1379.44188269913</v>
+        <v>1390.82641661259</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2328.90760780526</v>
+        <v>2329.25866009222</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1856.81199718015</v>
+        <v>1858.65339722933</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>185</v>
@@ -5010,13 +5010,13 @@
         <v>186</v>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1893.65312381858</v>
+        <v>1894.99070297252</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1893.65312381858</v>
+        <v>1894.99070297252</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1893.65312381858</v>
+        <v>1894.99070297252</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>187</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">0.8*D5+0.2*D8</f>
-        <v>2075.72669191032</v>
+        <v>2077.19981194967</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">B12/B13-1</f>
-        <v>-0.41611063518697</v>
+        <v>-0.415696255429067</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5237,11 +5237,11 @@
         <v>215</v>
       </c>
       <c r="B11" s="17" t="n">
-        <v>0.0756146197226035</v>
+        <v>0.0760014740197905</v>
       </c>
       <c r="C11" s="16" t="n">
         <f aca="false">(1+B11)/(1+$B$4)-1</f>
-        <v>0.0442860385656345</v>
+        <v>0.0446616252619325</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>216</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B16" s="18" t="n">
         <f aca="false">(C11-C10)*10000</f>
-        <v>82.8603856563451</v>
+        <v>86.6162526193252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">(C11-C7)*10000</f>
-        <v>192.860385656345</v>
+        <v>196.616252619325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5382,7 +5382,7 @@
         <v>232</v>
       </c>
       <c r="B4" s="17" t="n">
-        <v>0.0690189707474264</v>
+        <v>0.0726603209035945</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>233</v>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">B4*(1-B5)</f>
-        <v>0.0503838486456213</v>
+        <v>0.053042034259624</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(B6-B7)*10000</f>
-        <v>-215.956342826394</v>
+        <v>-189.374486686367</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">B14/$B$6</f>
-        <v>-0.0963477198056569</v>
+        <v>-0.0915192827688007</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>582787.013869718</v>
+        <v>592936.212324403</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>1917.83874034918</v>
+        <v>1911.50630339501</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">E14/$E$15-1</f>
-        <v>0.0328664093412301</v>
+        <v>0.0284361281368959</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5513,10 +5513,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>528835.311960595</v>
+        <v>540637.80850638</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1856.81199718015</v>
+        <v>1858.65339722932</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">E15/$E$15-1</f>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">B16/$B$6</f>
-        <v>0.0963477198056547</v>
+        <v>0.0915192827687986</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>474339.436361579</v>
+        <v>487810.963500129</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1784.87985066846</v>
+        <v>1796.13741969812</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">E16/$E$15-1</f>
-        <v>-0.0387395959423624</v>
+        <v>-0.0336350917413607</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">B17/$B$6</f>
-        <v>0.192695439611309</v>
+        <v>0.183038565537597</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>419299.387072671</v>
+        <v>434455.67730565</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1699.49188081559</v>
+        <v>1721.69849194288</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">E17/$E$15-1</f>
-        <v>-0.0847259262668888</v>
+        <v>-0.0736850159855503</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">B6</f>
-        <v>0.0503838486456213</v>
+        <v>0.053042034259624</v>
       </c>
       <c r="C23" s="16" t="n">
         <f aca="false">B7</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">100*((1-$A25/B$23)/($B$21-$A25))/(1/$B$21)</f>
-        <v>96.8003473141003</v>
+        <v>97.3348018032249</v>
       </c>
       <c r="C25" s="19" t="n">
         <f aca="false">100*((1-$A25/C$23)/($B$21-$A25))/(1/$B$21)</f>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">100*((1-$A26/B$23)/($B$21-$A26))/(1/$B$21)</f>
-        <v>93.0844507786669</v>
+        <v>94.239590629436</v>
       </c>
       <c r="C26" s="19" t="n">
         <f aca="false">100*((1-$A26/C$23)/($B$21-$A26))/(1/$B$21)</f>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">100*((1-$A27/B$23)/($B$21-$A27))/(1/$B$21)</f>
-        <v>88.7164078311448</v>
+        <v>90.6011644219682</v>
       </c>
       <c r="C27" s="19" t="n">
         <f aca="false">100*((1-$A27/C$23)/($B$21-$A27))/(1/$B$21)</f>
@@ -5911,15 +5911,15 @@
         <v>0</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1888.8</v>
+        <v>1892.2</v>
       </c>
       <c r="E15" s="12" t="n">
         <f aca="false">0.8*D15+0.2*2951.38547083101</f>
-        <v>2101.3170941662</v>
+        <v>2104.0370941662</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">E15/$E$17-1</f>
-        <v>0.0123330872361886</v>
+        <v>0.0129017530426674</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5934,15 +5934,15 @@
         <v>0.0780217040239421</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1872.8</v>
+        <v>1875.4</v>
       </c>
       <c r="E16" s="12" t="n">
         <f aca="false">0.8*D16+0.2*2951.38547083101</f>
-        <v>2088.5170941662</v>
+        <v>2090.5970941662</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">E16/$E$17-1</f>
-        <v>0.00616654361809421</v>
+        <v>0.00643162017350885</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5957,11 +5957,11 @@
         <v>0.156043408047884</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>1856.8</v>
+        <v>1858.7</v>
       </c>
       <c r="E17" s="12" t="n">
         <f aca="false">0.8*D17+0.2*2951.38547083101</f>
-        <v>2075.7170941662</v>
+        <v>2077.2370941662</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">E17/$E$17-1</f>
@@ -5980,15 +5980,15 @@
         <v>0.234065112071826</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>1840.8</v>
+        <v>1841.9</v>
       </c>
       <c r="E18" s="12" t="n">
         <f aca="false">0.8*D18+0.2*2951.38547083101</f>
-        <v>2062.9170941662</v>
+        <v>2063.7970941662</v>
       </c>
       <c r="F18" s="14" t="n">
         <f aca="false">E18/$E$17-1</f>
-        <v>-0.00616654361809421</v>
+        <v>-0.00647013286915854</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6003,15 +6003,15 @@
         <v>0.312086816095768</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1824.8</v>
+        <v>1825.2</v>
       </c>
       <c r="E19" s="12" t="n">
         <f aca="false">0.8*D19+0.2*2951.38547083101</f>
-        <v>2050.1170941662</v>
+        <v>2050.4370941662</v>
       </c>
       <c r="F19" s="14" t="n">
         <f aca="false">E19/$E$17-1</f>
-        <v>-0.0123330872361888</v>
+        <v>-0.0129017530426673</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6132,7 +6132,7 @@
         <v>297</v>
       </c>
       <c r="B9" s="15" t="n">
-        <v>0.100857870301779</v>
+        <v>0.100782648605333</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
@@ -6144,7 +6144,7 @@
         <v>298</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>0.112715304010366</v>
+        <v>0.112715864805192</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14" t="s">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">(B9-B5)*10000</f>
-        <v>412.882003643318</v>
+        <v>412.129786678858</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/secciones/valuacion/modelos/Mallplaza_Figuras_Valuacion_recalc.xlsx
+++ b/secciones/valuacion/modelos/Mallplaza_Figuras_Valuacion_recalc.xlsx
@@ -2797,12 +2797,12 @@
         <v>3293.93264667804</v>
       </c>
       <c r="D26" s="12" t="n">
-        <f aca="false">0.8*1856.81199718015+0.2*C26</f>
-        <v>2144.23612707973</v>
+        <f aca="false">0.8*1858.65339722933+0.2*C26</f>
+        <v>2145.70924711907</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">D26/$D$27-1</f>
-        <v>0.0330050364705556</v>
+        <v>0.0329816297764358</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2818,8 +2818,8 @@
         <v>2951.385470831</v>
       </c>
       <c r="D27" s="12" t="n">
-        <f aca="false">0.8*1856.81199718015+0.2*C27</f>
-        <v>2075.72669191032</v>
+        <f aca="false">0.8*1858.65339722933+0.2*C27</f>
+        <v>2077.19981194967</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">D27/$D$27-1</f>
@@ -2839,12 +2839,12 @@
         <v>2723.02068693298</v>
       </c>
       <c r="D28" s="12" t="n">
-        <f aca="false">0.8*1856.81199718015+0.2*C28</f>
-        <v>2030.05373513072</v>
+        <f aca="false">0.8*1858.65339722933+0.2*C28</f>
+        <v>2031.52685517006</v>
       </c>
       <c r="E28" s="14" t="n">
         <f aca="false">D28/$D$27-1</f>
-        <v>-0.0220033576470374</v>
+        <v>-0.0219877531842908</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2860,12 +2860,12 @@
         <v>2494.65590303496</v>
       </c>
       <c r="D29" s="12" t="n">
-        <f aca="false">0.8*1856.81199718015+0.2*C29</f>
-        <v>1984.38077835111</v>
+        <f aca="false">0.8*1858.65339722933+0.2*C29</f>
+        <v>1985.85389839046</v>
       </c>
       <c r="E29" s="14" t="n">
         <f aca="false">D29/$D$27-1</f>
-        <v>-0.0440067152940746</v>
+        <v>-0.0439755063685815</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2881,12 +2881,12 @@
         <v>2152.10872718793</v>
       </c>
       <c r="D30" s="12" t="n">
-        <f aca="false">0.8*1856.81199718015+0.2*C30</f>
-        <v>1915.87134318171</v>
+        <f aca="false">0.8*1858.65339722933+0.2*C30</f>
+        <v>1917.34446322105</v>
       </c>
       <c r="E30" s="14" t="n">
         <f aca="false">D30/$D$27-1</f>
-        <v>-0.0770117517646305</v>
+        <v>-0.0769571361450174</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
